--- a/xls/square_un_16_tri3_24.xlsx
+++ b/xls/square_un_16_tri3_24.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>797</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>340</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>668</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>3738</v>
+      </c>
+      <c r="I22">
+        <v>-1.4307365667992194e-6</v>
+      </c>
+      <c r="J22">
+        <v>-0.0043420936246108596</v>
+      </c>
+      <c r="K22">
+        <v>3.15422320089683</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>797</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>340</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>741</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>4164</v>
+      </c>
+      <c r="I23">
+        <v>-1.2700045014606186e-7</v>
+      </c>
+      <c r="J23">
+        <v>-0.0002526595054416122</v>
+      </c>
+      <c r="K23">
+        <v>2.635575062718712</v>
+      </c>
+    </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>11</v>
       </c>
       <c r="B24">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-1.9855314130276567</v>
+        <v>-6.036794203791003e-8</v>
       </c>
       <c r="J24">
-        <v>-1.5676776680722755</v>
+        <v>-0.00011058520276168858</v>
       </c>
       <c r="K24">
-        <v>1.5490893015266254</v>
+        <v>2.452471185857365</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-0.8640089146325898</v>
+        <v>-2.4876631776040174e-8</v>
       </c>
       <c r="J25">
-        <v>-0.6774308161194482</v>
+        <v>-4.549099568422903e-5</v>
       </c>
       <c r="K25">
-        <v>3.2419048659726553</v>
+        <v>2.266240055931673</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-0.021302510732904092</v>
+        <v>-1.720610337565167e-8</v>
       </c>
       <c r="J26">
-        <v>-0.019393538947867286</v>
+        <v>-2.9921872399216547e-5</v>
       </c>
       <c r="K26">
-        <v>3.5170317920229297</v>
+        <v>2.17170102953485</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-0.002637822336852151</v>
+        <v>-1.2938713009752063e-8</v>
       </c>
       <c r="J27">
-        <v>-0.0025012505654837228</v>
+        <v>-2.2787123380187317e-5</v>
       </c>
       <c r="K27">
-        <v>3.1285910516316755</v>
+        <v>2.116405644684597</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-0.0008214179648832299</v>
+        <v>-1.0557953137560072e-8</v>
       </c>
       <c r="J28">
-        <v>-0.0009848327454564452</v>
+        <v>-1.9313194546864986e-5</v>
       </c>
       <c r="K28">
-        <v>2.9811111279107516</v>
+        <v>2.083842810290002</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-0.00037815213109995086</v>
+        <v>-9.911864568427162e-9</v>
       </c>
       <c r="J29">
-        <v>-0.0004515844253263268</v>
+        <v>-1.7952517498936763e-5</v>
       </c>
       <c r="K29">
-        <v>2.814028903913353</v>
+        <v>2.0656261369352538</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-0.0002682889754736187</v>
+        <v>-6.291517424758356e-9</v>
       </c>
       <c r="J30">
-        <v>-0.0003127602362292251</v>
+        <v>-1.1088619670843426e-5</v>
       </c>
       <c r="K30">
-        <v>2.731924936742401</v>
+        <v>1.958358683426953</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-0.00018773744724939802</v>
+        <v>-5.393684230471531e-9</v>
       </c>
       <c r="J31">
-        <v>-0.0002175365492982934</v>
+        <v>-9.716422242936809e-6</v>
       </c>
       <c r="K31">
-        <v>2.6550491982198756</v>
+        <v>1.9345110178511271</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>728</v>
+        <v>797</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-0.00013188132955507958</v>
+        <v>-4.480245808652065e-9</v>
       </c>
       <c r="J32">
-        <v>-0.00015648745603374952</v>
+        <v>-8.394200407499443e-6</v>
       </c>
       <c r="K32">
-        <v>2.5868546106974057</v>
+        <v>1.9062738694733665</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_24.xlsx
+++ b/xls/square_un_16_tri3_24.xlsx
@@ -482,13 +482,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-1.4307365667992194e-6</v>
+        <v>-1.0229832310261713</v>
       </c>
       <c r="J22">
-        <v>-0.0043420936246108596</v>
+        <v>-0.8590843909132878</v>
       </c>
       <c r="K22">
-        <v>3.15422320089683</v>
+        <v>1.863156156089104</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -517,13 +517,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-1.2700045014606186e-7</v>
+        <v>-0.0012865071587190228</v>
       </c>
       <c r="J23">
-        <v>-0.0002526595054416122</v>
+        <v>-0.0017452916998060152</v>
       </c>
       <c r="K23">
-        <v>2.635575062718712</v>
+        <v>3.042683029855767</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -552,13 +552,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-6.036794203791003e-8</v>
+        <v>-0.00013563318420375869</v>
       </c>
       <c r="J24">
-        <v>-0.00011058520276168858</v>
+        <v>-0.00015823163802804722</v>
       </c>
       <c r="K24">
-        <v>2.452471185857365</v>
+        <v>2.581593806193437</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -587,13 +587,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-2.4876631776040174e-8</v>
+        <v>-3.0331262345789625e-5</v>
       </c>
       <c r="J25">
-        <v>-4.549099568422903e-5</v>
+        <v>-4.5004773212917946e-5</v>
       </c>
       <c r="K25">
-        <v>2.266240055931673</v>
+        <v>2.344980909462294</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -622,13 +622,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-1.720610337565167e-8</v>
+        <v>-2.8878620818697242e-5</v>
       </c>
       <c r="J26">
-        <v>-2.9921872399216547e-5</v>
+        <v>-3.150758982076283e-5</v>
       </c>
       <c r="K26">
-        <v>2.17170102953485</v>
+        <v>2.2201741194399385</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -657,13 +657,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-1.2938713009752063e-8</v>
+        <v>-2.2872884617184254e-5</v>
       </c>
       <c r="J27">
-        <v>-2.2787123380187317e-5</v>
+        <v>-2.3262660468687156e-5</v>
       </c>
       <c r="K27">
-        <v>2.116405644684597</v>
+        <v>2.1417122654057157</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -692,13 +692,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-1.0557953137560072e-8</v>
+        <v>-2.2332209511816203e-5</v>
       </c>
       <c r="J28">
-        <v>-1.9313194546864986e-5</v>
+        <v>-2.1713569653105245e-5</v>
       </c>
       <c r="K28">
-        <v>2.083842810290002</v>
+        <v>2.109942076995779</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -727,13 +727,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-9.911864568427162e-9</v>
+        <v>-2.2460596725532304e-5</v>
       </c>
       <c r="J29">
-        <v>-1.7952517498936763e-5</v>
+        <v>-2.09037330783901e-5</v>
       </c>
       <c r="K29">
-        <v>2.0656261369352538</v>
+        <v>2.089522530864117</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -762,13 +762,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-6.291517424758356e-9</v>
+        <v>-1.2179235394355045e-5</v>
       </c>
       <c r="J30">
-        <v>-1.1088619670843426e-5</v>
+        <v>-1.1997599908278753e-5</v>
       </c>
       <c r="K30">
-        <v>1.958358683426953</v>
+        <v>1.985388760315963</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -797,13 +797,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-5.393684230471531e-9</v>
+        <v>-1.1300595815201808e-5</v>
       </c>
       <c r="J31">
-        <v>-9.716422242936809e-6</v>
+        <v>-1.0686201007764115e-5</v>
       </c>
       <c r="K31">
-        <v>1.9345110178511271</v>
+        <v>1.950525824134312</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -832,13 +832,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-4.480245808652065e-9</v>
+        <v>-9.33358062519611e-6</v>
       </c>
       <c r="J32">
-        <v>-8.394200407499443e-6</v>
+        <v>-9.06327490022867e-6</v>
       </c>
       <c r="K32">
-        <v>1.9062738694733665</v>
+        <v>1.9216842613344591</v>
       </c>
     </row>
   </sheetData>
